--- a/vaultwarden_export.xlsx
+++ b/vaultwarden_export.xlsx
@@ -416,43 +416,43 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Наименование коллекции (collection_name)</t>
+          <t>Collection Name (collection_name)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Наименование записи (name)</t>
+          <t>Item Name (name)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Комментарий к записи (note)</t>
+          <t>Item Note (note)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>username (login)</t>
+          <t>Username (login)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Пароль(password)</t>
+          <t>Password (password)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Длина пароля</t>
+          <t>Password Length</t>
         </is>
       </c>
     </row>
